--- a/VerveStacks_GRC/vt_vervestacks_GRC_v1.xlsx
+++ b/VerveStacks_GRC/vt_vervestacks_GRC_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GRC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD7FF0C8-3229-4CF5-979E-C0231E8B4442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D971027-5A0B-48FF-9E84-C278BD9D3E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{309993F2-FD95-452D-B397-D95F479123E4}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D22D23F0-B62A-45F5-8339-369E740FFA30}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -1295,7 +1295,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE1EC989-A18C-4541-B904-6D1690861314}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E51CE55-B58D-432A-97B0-2AC8EAE9E766}">
   <dimension ref="B9:T62"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4281,7 +4281,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60FBD6D-9A7D-4BF3-8907-009D83983FA4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B43A64A7-4991-45FB-80E7-38C6130E6F1D}">
   <dimension ref="B9:T124"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_GRC/vt_vervestacks_GRC_v1.xlsx
+++ b/VerveStacks_GRC/vt_vervestacks_GRC_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GRC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D971027-5A0B-48FF-9E84-C278BD9D3E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2AE391A-1884-4767-A36B-B92E16F32DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D22D23F0-B62A-45F5-8339-369E740FFA30}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0612527A-765D-4B58-8845-655209E58881}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -1295,7 +1295,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E51CE55-B58D-432A-97B0-2AC8EAE9E766}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6D4DEB4-0360-424D-A6BF-F618656B875F}">
   <dimension ref="B9:T62"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1374,19 +1374,19 @@
         <v>14</v>
       </c>
       <c r="E11">
-        <v>0.178087</v>
+        <v>8.7673600000000018E-2</v>
       </c>
       <c r="F11">
-        <v>2757</v>
+        <v>3583</v>
       </c>
       <c r="G11">
-        <v>39.200000000000003</v>
+        <v>49</v>
       </c>
       <c r="H11">
-        <v>3.35</v>
+        <v>4.59</v>
       </c>
       <c r="I11">
-        <v>0.63080000000000003</v>
+        <v>0.5605</v>
       </c>
       <c r="J11" t="s">
         <v>17</v>
@@ -1430,19 +1430,19 @@
         <v>14</v>
       </c>
       <c r="E12">
-        <v>0.178087</v>
+        <v>8.7673600000000018E-2</v>
       </c>
       <c r="F12">
-        <v>2757</v>
+        <v>3583</v>
       </c>
       <c r="G12">
-        <v>39.200000000000003</v>
+        <v>49</v>
       </c>
       <c r="H12">
-        <v>3.35</v>
+        <v>4.59</v>
       </c>
       <c r="I12">
-        <v>0.63080000000000003</v>
+        <v>0.5605</v>
       </c>
       <c r="J12" t="s">
         <v>18</v>
@@ -1486,7 +1486,7 @@
         <v>14</v>
       </c>
       <c r="E13">
-        <v>0.11272320000000002</v>
+        <v>9.0178560000000019E-2</v>
       </c>
       <c r="F13">
         <v>3583</v>
@@ -1542,19 +1542,19 @@
         <v>14</v>
       </c>
       <c r="E14">
-        <v>0.19843979999999997</v>
+        <v>0.13015080000000001</v>
       </c>
       <c r="F14">
-        <v>2757</v>
+        <v>3144</v>
       </c>
       <c r="G14">
-        <v>39.200000000000003</v>
+        <v>43.8</v>
       </c>
       <c r="H14">
-        <v>3.35</v>
+        <v>3.94</v>
       </c>
       <c r="I14">
-        <v>0.63080000000000003</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J14" t="s">
         <v>19</v>
@@ -1598,19 +1598,19 @@
         <v>14</v>
       </c>
       <c r="E15">
-        <v>0.20098390000000002</v>
+        <v>0.13181940000000003</v>
       </c>
       <c r="F15">
-        <v>2757</v>
+        <v>3144</v>
       </c>
       <c r="G15">
-        <v>39.200000000000003</v>
+        <v>43.8</v>
       </c>
       <c r="H15">
-        <v>3.35</v>
+        <v>3.94</v>
       </c>
       <c r="I15">
-        <v>0.63080000000000003</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J15" t="s">
         <v>20</v>
@@ -1654,7 +1654,7 @@
         <v>14</v>
       </c>
       <c r="E16">
-        <v>0.34972104999999998</v>
+        <v>0.27977684000000003</v>
       </c>
       <c r="F16">
         <v>1967</v>
@@ -1710,7 +1710,7 @@
         <v>14</v>
       </c>
       <c r="E17">
-        <v>0.52272499999999988</v>
+        <v>0.41818</v>
       </c>
       <c r="F17">
         <v>1365</v>
@@ -1766,7 +1766,7 @@
         <v>14</v>
       </c>
       <c r="E18">
-        <v>0.49118125000000001</v>
+        <v>0.39294500000000004</v>
       </c>
       <c r="F18">
         <v>1365</v>
@@ -1822,7 +1822,7 @@
         <v>14</v>
       </c>
       <c r="E19">
-        <v>0.54075000000000006</v>
+        <v>0.43259999999999998</v>
       </c>
       <c r="F19">
         <v>1365</v>
@@ -1878,7 +1878,7 @@
         <v>14</v>
       </c>
       <c r="E20">
-        <v>0.52272499999999988</v>
+        <v>0.41818</v>
       </c>
       <c r="F20">
         <v>1365</v>
@@ -1934,7 +1934,7 @@
         <v>14</v>
       </c>
       <c r="E21">
-        <v>0.52272499999999988</v>
+        <v>0.41817999999999989</v>
       </c>
       <c r="F21">
         <v>1365</v>
@@ -1990,7 +1990,7 @@
         <v>14</v>
       </c>
       <c r="E22">
-        <v>0.49118125000000001</v>
+        <v>0.39294500000000004</v>
       </c>
       <c r="F22">
         <v>1365</v>
@@ -2046,7 +2046,7 @@
         <v>14</v>
       </c>
       <c r="E23">
-        <v>0.47315625000000006</v>
+        <v>0.37852500000000006</v>
       </c>
       <c r="F23">
         <v>1365</v>
@@ -2102,7 +2102,7 @@
         <v>14</v>
       </c>
       <c r="E24">
-        <v>0.49118125000000001</v>
+        <v>0.39294499999999999</v>
       </c>
       <c r="F24">
         <v>1365</v>
@@ -2158,7 +2158,7 @@
         <v>14</v>
       </c>
       <c r="E25">
-        <v>0.49118125000000001</v>
+        <v>0.39294500000000004</v>
       </c>
       <c r="F25">
         <v>1365</v>
@@ -2214,7 +2214,7 @@
         <v>14</v>
       </c>
       <c r="E26">
-        <v>0.49118125000000001</v>
+        <v>0.39294500000000004</v>
       </c>
       <c r="F26">
         <v>1365</v>
@@ -2270,7 +2270,7 @@
         <v>14</v>
       </c>
       <c r="E27">
-        <v>0.49118125000000001</v>
+        <v>0.39294500000000004</v>
       </c>
       <c r="F27">
         <v>1365</v>
@@ -2326,7 +2326,7 @@
         <v>14</v>
       </c>
       <c r="E28">
-        <v>0.54075000000000006</v>
+        <v>0.43259999999999998</v>
       </c>
       <c r="F28">
         <v>1365</v>
@@ -2382,7 +2382,7 @@
         <v>14</v>
       </c>
       <c r="E29">
-        <v>0.54075000000000006</v>
+        <v>0.43259999999999998</v>
       </c>
       <c r="F29">
         <v>1365</v>
@@ -2438,7 +2438,7 @@
         <v>14</v>
       </c>
       <c r="E30">
-        <v>0.52272499999999988</v>
+        <v>0.41818</v>
       </c>
       <c r="F30">
         <v>1365</v>
@@ -2494,7 +2494,7 @@
         <v>14</v>
       </c>
       <c r="E31">
-        <v>0.54075000000000006</v>
+        <v>0.43259999999999998</v>
       </c>
       <c r="F31">
         <v>1365</v>
@@ -2550,7 +2550,7 @@
         <v>14</v>
       </c>
       <c r="E32">
-        <v>0.25235000000000002</v>
+        <v>0.20188000000000003</v>
       </c>
       <c r="F32">
         <v>1365</v>
@@ -2606,7 +2606,7 @@
         <v>14</v>
       </c>
       <c r="E33">
-        <v>0.25235000000000002</v>
+        <v>0.20188000000000003</v>
       </c>
       <c r="F33">
         <v>1365</v>
@@ -2662,7 +2662,7 @@
         <v>14</v>
       </c>
       <c r="E34">
-        <v>0.25235000000000002</v>
+        <v>0.20188000000000003</v>
       </c>
       <c r="F34">
         <v>1365</v>
@@ -4281,7 +4281,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B43A64A7-4991-45FB-80E7-38C6130E6F1D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BCE7E01-1F78-4BBE-9978-D9AD0B9ED710}">
   <dimension ref="B9:T124"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4419,7 +4419,7 @@
         <v>0.89500000000000024</v>
       </c>
       <c r="G12">
-        <v>0.37080000000000002</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H12">
         <v>2200</v>
@@ -4472,7 +4472,7 @@
         <v>0.31</v>
       </c>
       <c r="G13">
-        <v>0.36049999999999999</v>
+        <v>0.28839999999999999</v>
       </c>
       <c r="H13">
         <v>2200</v>
@@ -4525,7 +4525,7 @@
         <v>0.31</v>
       </c>
       <c r="G14">
-        <v>0.36049999999999999</v>
+        <v>0.28839999999999999</v>
       </c>
       <c r="H14">
         <v>2200</v>
@@ -4578,7 +4578,7 @@
         <v>0.375</v>
       </c>
       <c r="G15">
-        <v>0.40169999999999995</v>
+        <v>0.32136000000000003</v>
       </c>
       <c r="H15">
         <v>2420</v>
@@ -4631,7 +4631,7 @@
         <v>0.33</v>
       </c>
       <c r="G16">
-        <v>0.40685000000000004</v>
+        <v>0.32548000000000005</v>
       </c>
       <c r="H16">
         <v>2420</v>
@@ -4684,7 +4684,7 @@
         <v>0.66</v>
       </c>
       <c r="G17">
-        <v>0.45835000000000004</v>
+        <v>0.36668000000000006</v>
       </c>
       <c r="H17">
         <v>2640</v>
@@ -4737,7 +4737,7 @@
         <v>1.0463999999999993</v>
       </c>
       <c r="G18">
-        <v>0.61799999999999999</v>
+        <v>0.49440000000000001</v>
       </c>
       <c r="H18">
         <v>1100</v>
@@ -4790,7 +4790,7 @@
         <v>0.44400000000000001</v>
       </c>
       <c r="G19">
-        <v>0.59739999999999993</v>
+        <v>0.47791999999999996</v>
       </c>
       <c r="H19">
         <v>1100</v>
@@ -4843,7 +4843,7 @@
         <v>0.33400000000000002</v>
       </c>
       <c r="G20">
-        <v>0.56135000000000002</v>
+        <v>0.44908000000000003</v>
       </c>
       <c r="H20">
         <v>1100</v>
@@ -4896,7 +4896,7 @@
         <v>0.82599999999999996</v>
       </c>
       <c r="G21">
-        <v>0.61799999999999999</v>
+        <v>0.49439999999999995</v>
       </c>
       <c r="H21">
         <v>1100</v>
@@ -4949,7 +4949,7 @@
         <v>0.41699999999999998</v>
       </c>
       <c r="G22">
-        <v>0.59739999999999993</v>
+        <v>0.47791999999999996</v>
       </c>
       <c r="H22">
         <v>1100</v>
@@ -5002,7 +5002,7 @@
         <v>0.43660000000000004</v>
       </c>
       <c r="G23">
-        <v>0.59739999999999993</v>
+        <v>0.4779199999999999</v>
       </c>
       <c r="H23">
         <v>1100</v>
@@ -5055,7 +5055,7 @@
         <v>0.48499999999999999</v>
       </c>
       <c r="G24">
-        <v>0.56135000000000002</v>
+        <v>0.44908000000000003</v>
       </c>
       <c r="H24">
         <v>1100</v>
@@ -5108,7 +5108,7 @@
         <v>0.53600000000000003</v>
       </c>
       <c r="G25">
-        <v>0.54075000000000006</v>
+        <v>0.4326000000000001</v>
       </c>
       <c r="H25">
         <v>1100</v>
@@ -5161,7 +5161,7 @@
         <v>0.378</v>
       </c>
       <c r="G26">
-        <v>0.56135000000000002</v>
+        <v>0.44907999999999998</v>
       </c>
       <c r="H26">
         <v>1100</v>
@@ -5214,7 +5214,7 @@
         <v>0.42</v>
       </c>
       <c r="G27">
-        <v>0.56135000000000002</v>
+        <v>0.44908000000000003</v>
       </c>
       <c r="H27">
         <v>1100</v>
@@ -5267,7 +5267,7 @@
         <v>0.42</v>
       </c>
       <c r="G28">
-        <v>0.56135000000000002</v>
+        <v>0.44908000000000003</v>
       </c>
       <c r="H28">
         <v>1100</v>
@@ -5320,7 +5320,7 @@
         <v>0.435</v>
       </c>
       <c r="G29">
-        <v>0.56135000000000002</v>
+        <v>0.44908000000000003</v>
       </c>
       <c r="H29">
         <v>1100</v>
@@ -5373,7 +5373,7 @@
         <v>0.84</v>
       </c>
       <c r="G30">
-        <v>0.61799999999999999</v>
+        <v>0.49440000000000001</v>
       </c>
       <c r="H30">
         <v>1100</v>
@@ -5426,7 +5426,7 @@
         <v>0.877</v>
       </c>
       <c r="G31">
-        <v>0.61799999999999999</v>
+        <v>0.49440000000000001</v>
       </c>
       <c r="H31">
         <v>1100</v>
@@ -5479,7 +5479,7 @@
         <v>0.81100000000000005</v>
       </c>
       <c r="G32">
-        <v>0.59739999999999993</v>
+        <v>0.47791999999999996</v>
       </c>
       <c r="H32">
         <v>1100</v>
@@ -5532,7 +5532,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="G33">
-        <v>0.28840000000000005</v>
+        <v>0.23072000000000004</v>
       </c>
       <c r="H33">
         <v>1188</v>
@@ -5585,7 +5585,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="G34">
-        <v>0.28840000000000005</v>
+        <v>0.23072000000000004</v>
       </c>
       <c r="H34">
         <v>1188</v>
@@ -5638,7 +5638,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="G35">
-        <v>0.28840000000000005</v>
+        <v>0.23072000000000004</v>
       </c>
       <c r="H35">
         <v>1188</v>

--- a/VerveStacks_GRC/vt_vervestacks_GRC_v1.xlsx
+++ b/VerveStacks_GRC/vt_vervestacks_GRC_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GRC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2AE391A-1884-4767-A36B-B92E16F32DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB8904B7-1F5D-4A8E-A9AA-90C56C324AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0612527A-765D-4B58-8845-655209E58881}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4299DD26-1EC4-4767-ABE0-B1F85C48E350}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -1295,7 +1295,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6D4DEB4-0360-424D-A6BF-F618656B875F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{731C5DDE-A225-4454-AE32-3E6BED5F8C03}">
   <dimension ref="B9:T62"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1374,7 +1374,7 @@
         <v>14</v>
       </c>
       <c r="E11">
-        <v>8.7673600000000018E-2</v>
+        <v>8.5481760000000018E-2</v>
       </c>
       <c r="F11">
         <v>3583</v>
@@ -1430,7 +1430,7 @@
         <v>14</v>
       </c>
       <c r="E12">
-        <v>8.7673600000000018E-2</v>
+        <v>8.5481760000000018E-2</v>
       </c>
       <c r="F12">
         <v>3583</v>
@@ -1486,7 +1486,7 @@
         <v>14</v>
       </c>
       <c r="E13">
-        <v>9.0178560000000019E-2</v>
+        <v>8.7924096000000021E-2</v>
       </c>
       <c r="F13">
         <v>3583</v>
@@ -1542,7 +1542,7 @@
         <v>14</v>
       </c>
       <c r="E14">
-        <v>0.13015080000000001</v>
+        <v>0.12689702999999999</v>
       </c>
       <c r="F14">
         <v>3144</v>
@@ -1598,7 +1598,7 @@
         <v>14</v>
       </c>
       <c r="E15">
-        <v>0.13181940000000003</v>
+        <v>0.12852391500000002</v>
       </c>
       <c r="F15">
         <v>3144</v>
@@ -1654,7 +1654,7 @@
         <v>14</v>
       </c>
       <c r="E16">
-        <v>0.27977684000000003</v>
+        <v>0.272782419</v>
       </c>
       <c r="F16">
         <v>1967</v>
@@ -1710,7 +1710,7 @@
         <v>14</v>
       </c>
       <c r="E17">
-        <v>0.41818</v>
+        <v>0.40772549999999996</v>
       </c>
       <c r="F17">
         <v>1365</v>
@@ -1766,7 +1766,7 @@
         <v>14</v>
       </c>
       <c r="E18">
-        <v>0.39294500000000004</v>
+        <v>0.38312137500000004</v>
       </c>
       <c r="F18">
         <v>1365</v>
@@ -1822,7 +1822,7 @@
         <v>14</v>
       </c>
       <c r="E19">
-        <v>0.43259999999999998</v>
+        <v>0.42178500000000002</v>
       </c>
       <c r="F19">
         <v>1365</v>
@@ -1878,7 +1878,7 @@
         <v>14</v>
       </c>
       <c r="E20">
-        <v>0.41818</v>
+        <v>0.40772549999999996</v>
       </c>
       <c r="F20">
         <v>1365</v>
@@ -1934,7 +1934,7 @@
         <v>14</v>
       </c>
       <c r="E21">
-        <v>0.41817999999999989</v>
+        <v>0.40772549999999996</v>
       </c>
       <c r="F21">
         <v>1365</v>
@@ -1990,7 +1990,7 @@
         <v>14</v>
       </c>
       <c r="E22">
-        <v>0.39294500000000004</v>
+        <v>0.38312137500000004</v>
       </c>
       <c r="F22">
         <v>1365</v>
@@ -2046,7 +2046,7 @@
         <v>14</v>
       </c>
       <c r="E23">
-        <v>0.37852500000000006</v>
+        <v>0.36906187500000009</v>
       </c>
       <c r="F23">
         <v>1365</v>
@@ -2102,7 +2102,7 @@
         <v>14</v>
       </c>
       <c r="E24">
-        <v>0.39294499999999999</v>
+        <v>0.38312137500000004</v>
       </c>
       <c r="F24">
         <v>1365</v>
@@ -2158,7 +2158,7 @@
         <v>14</v>
       </c>
       <c r="E25">
-        <v>0.39294500000000004</v>
+        <v>0.38312137500000004</v>
       </c>
       <c r="F25">
         <v>1365</v>
@@ -2214,7 +2214,7 @@
         <v>14</v>
       </c>
       <c r="E26">
-        <v>0.39294500000000004</v>
+        <v>0.38312137500000004</v>
       </c>
       <c r="F26">
         <v>1365</v>
@@ -2270,7 +2270,7 @@
         <v>14</v>
       </c>
       <c r="E27">
-        <v>0.39294500000000004</v>
+        <v>0.38312137500000004</v>
       </c>
       <c r="F27">
         <v>1365</v>
@@ -2326,7 +2326,7 @@
         <v>14</v>
       </c>
       <c r="E28">
-        <v>0.43259999999999998</v>
+        <v>0.42178500000000002</v>
       </c>
       <c r="F28">
         <v>1365</v>
@@ -2382,7 +2382,7 @@
         <v>14</v>
       </c>
       <c r="E29">
-        <v>0.43259999999999998</v>
+        <v>0.42178500000000008</v>
       </c>
       <c r="F29">
         <v>1365</v>
@@ -2438,7 +2438,7 @@
         <v>14</v>
       </c>
       <c r="E30">
-        <v>0.41818</v>
+        <v>0.40772549999999996</v>
       </c>
       <c r="F30">
         <v>1365</v>
@@ -2494,7 +2494,7 @@
         <v>14</v>
       </c>
       <c r="E31">
-        <v>0.43259999999999998</v>
+        <v>0.42178500000000002</v>
       </c>
       <c r="F31">
         <v>1365</v>
@@ -2550,7 +2550,7 @@
         <v>14</v>
       </c>
       <c r="E32">
-        <v>0.20188000000000003</v>
+        <v>0.19683300000000004</v>
       </c>
       <c r="F32">
         <v>1365</v>
@@ -2606,7 +2606,7 @@
         <v>14</v>
       </c>
       <c r="E33">
-        <v>0.20188000000000003</v>
+        <v>0.19683300000000004</v>
       </c>
       <c r="F33">
         <v>1365</v>
@@ -2662,7 +2662,7 @@
         <v>14</v>
       </c>
       <c r="E34">
-        <v>0.20188000000000003</v>
+        <v>0.19683300000000004</v>
       </c>
       <c r="F34">
         <v>1365</v>
@@ -4281,7 +4281,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BCE7E01-1F78-4BBE-9978-D9AD0B9ED710}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03944C91-5507-487B-98F2-071AE5BE82D9}">
   <dimension ref="B9:T124"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4419,7 +4419,7 @@
         <v>0.89500000000000024</v>
       </c>
       <c r="G12">
-        <v>0.29664000000000001</v>
+        <v>0.28922400000000004</v>
       </c>
       <c r="H12">
         <v>2200</v>
@@ -4472,7 +4472,7 @@
         <v>0.31</v>
       </c>
       <c r="G13">
-        <v>0.28839999999999999</v>
+        <v>0.28119</v>
       </c>
       <c r="H13">
         <v>2200</v>
@@ -4525,7 +4525,7 @@
         <v>0.31</v>
       </c>
       <c r="G14">
-        <v>0.28839999999999999</v>
+        <v>0.28119</v>
       </c>
       <c r="H14">
         <v>2200</v>
@@ -4578,7 +4578,7 @@
         <v>0.375</v>
       </c>
       <c r="G15">
-        <v>0.32136000000000003</v>
+        <v>0.31332599999999999</v>
       </c>
       <c r="H15">
         <v>2420</v>
@@ -4631,7 +4631,7 @@
         <v>0.33</v>
       </c>
       <c r="G16">
-        <v>0.32548000000000005</v>
+        <v>0.31734300000000004</v>
       </c>
       <c r="H16">
         <v>2420</v>
@@ -4684,7 +4684,7 @@
         <v>0.66</v>
       </c>
       <c r="G17">
-        <v>0.36668000000000006</v>
+        <v>0.35751300000000003</v>
       </c>
       <c r="H17">
         <v>2640</v>
@@ -4737,7 +4737,7 @@
         <v>1.0463999999999993</v>
       </c>
       <c r="G18">
-        <v>0.49440000000000001</v>
+        <v>0.48204000000000002</v>
       </c>
       <c r="H18">
         <v>1100</v>
@@ -4790,7 +4790,7 @@
         <v>0.44400000000000001</v>
       </c>
       <c r="G19">
-        <v>0.47791999999999996</v>
+        <v>0.46597199999999994</v>
       </c>
       <c r="H19">
         <v>1100</v>
@@ -4843,7 +4843,7 @@
         <v>0.33400000000000002</v>
       </c>
       <c r="G20">
-        <v>0.44908000000000003</v>
+        <v>0.43785300000000005</v>
       </c>
       <c r="H20">
         <v>1100</v>
@@ -4896,7 +4896,7 @@
         <v>0.82599999999999996</v>
       </c>
       <c r="G21">
-        <v>0.49439999999999995</v>
+        <v>0.48204000000000002</v>
       </c>
       <c r="H21">
         <v>1100</v>
@@ -4949,7 +4949,7 @@
         <v>0.41699999999999998</v>
       </c>
       <c r="G22">
-        <v>0.47791999999999996</v>
+        <v>0.46597199999999994</v>
       </c>
       <c r="H22">
         <v>1100</v>
@@ -5002,7 +5002,7 @@
         <v>0.43660000000000004</v>
       </c>
       <c r="G23">
-        <v>0.4779199999999999</v>
+        <v>0.46597199999999994</v>
       </c>
       <c r="H23">
         <v>1100</v>
@@ -5055,7 +5055,7 @@
         <v>0.48499999999999999</v>
       </c>
       <c r="G24">
-        <v>0.44908000000000003</v>
+        <v>0.43785300000000005</v>
       </c>
       <c r="H24">
         <v>1100</v>
@@ -5108,7 +5108,7 @@
         <v>0.53600000000000003</v>
       </c>
       <c r="G25">
-        <v>0.4326000000000001</v>
+        <v>0.42178500000000008</v>
       </c>
       <c r="H25">
         <v>1100</v>
@@ -5161,7 +5161,7 @@
         <v>0.378</v>
       </c>
       <c r="G26">
-        <v>0.44907999999999998</v>
+        <v>0.43785300000000005</v>
       </c>
       <c r="H26">
         <v>1100</v>
@@ -5214,7 +5214,7 @@
         <v>0.42</v>
       </c>
       <c r="G27">
-        <v>0.44908000000000003</v>
+        <v>0.43785300000000005</v>
       </c>
       <c r="H27">
         <v>1100</v>
@@ -5267,7 +5267,7 @@
         <v>0.42</v>
       </c>
       <c r="G28">
-        <v>0.44908000000000003</v>
+        <v>0.43785300000000005</v>
       </c>
       <c r="H28">
         <v>1100</v>
@@ -5320,7 +5320,7 @@
         <v>0.435</v>
       </c>
       <c r="G29">
-        <v>0.44908000000000003</v>
+        <v>0.43785300000000005</v>
       </c>
       <c r="H29">
         <v>1100</v>
@@ -5373,7 +5373,7 @@
         <v>0.84</v>
       </c>
       <c r="G30">
-        <v>0.49440000000000001</v>
+        <v>0.48204000000000002</v>
       </c>
       <c r="H30">
         <v>1100</v>
@@ -5426,7 +5426,7 @@
         <v>0.877</v>
       </c>
       <c r="G31">
-        <v>0.49440000000000001</v>
+        <v>0.48204000000000008</v>
       </c>
       <c r="H31">
         <v>1100</v>
@@ -5479,7 +5479,7 @@
         <v>0.81100000000000005</v>
       </c>
       <c r="G32">
-        <v>0.47791999999999996</v>
+        <v>0.46597199999999994</v>
       </c>
       <c r="H32">
         <v>1100</v>
@@ -5532,7 +5532,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="G33">
-        <v>0.23072000000000004</v>
+        <v>0.22495200000000004</v>
       </c>
       <c r="H33">
         <v>1188</v>
@@ -5585,7 +5585,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="G34">
-        <v>0.23072000000000004</v>
+        <v>0.22495200000000004</v>
       </c>
       <c r="H34">
         <v>1188</v>
@@ -5638,7 +5638,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="G35">
-        <v>0.23072000000000004</v>
+        <v>0.22495200000000004</v>
       </c>
       <c r="H35">
         <v>1188</v>

--- a/VerveStacks_GRC/vt_vervestacks_GRC_v1.xlsx
+++ b/VerveStacks_GRC/vt_vervestacks_GRC_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GRC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB8904B7-1F5D-4A8E-A9AA-90C56C324AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6EC29549-4589-4228-80AE-DD39422C1650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4299DD26-1EC4-4767-ABE0-B1F85C48E350}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{3B746008-3BC5-48B6-AB27-FB6BB85943CF}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -1295,7 +1295,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{731C5DDE-A225-4454-AE32-3E6BED5F8C03}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F7864F0-0735-4724-963C-518BB18C9FAA}">
   <dimension ref="B9:T62"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4281,7 +4281,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03944C91-5507-487B-98F2-071AE5BE82D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD445F59-4A10-4FF0-80B5-2184A2348430}">
   <dimension ref="B9:T124"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_GRC/vt_vervestacks_GRC_v1.xlsx
+++ b/VerveStacks_GRC/vt_vervestacks_GRC_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GRC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6EC29549-4589-4228-80AE-DD39422C1650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B3A0345-39F8-4FCE-B0DE-EEFA73516610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{3B746008-3BC5-48B6-AB27-FB6BB85943CF}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{262781E9-7CE6-4CF1-84F4-03993671DA64}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -1295,7 +1295,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F7864F0-0735-4724-963C-518BB18C9FAA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C2AE76D-B5E7-4F9D-99A6-B1749C5525BC}">
   <dimension ref="B9:T62"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2718,7 +2718,7 @@
         <v>14</v>
       </c>
       <c r="E35">
-        <v>0.43259999999999998</v>
+        <v>0.33742800000000001</v>
       </c>
       <c r="F35">
         <v>1365</v>
@@ -2774,7 +2774,7 @@
         <v>14</v>
       </c>
       <c r="E36">
-        <v>0.36951250000000002</v>
+        <v>0.28821975</v>
       </c>
       <c r="F36">
         <v>1365</v>
@@ -2830,7 +2830,7 @@
         <v>14</v>
       </c>
       <c r="E37">
-        <v>0.36951250000000002</v>
+        <v>0.28821975</v>
       </c>
       <c r="F37">
         <v>1365</v>
@@ -2886,7 +2886,7 @@
         <v>14</v>
       </c>
       <c r="E38">
-        <v>0.24333750000000001</v>
+        <v>0.18980325000000003</v>
       </c>
       <c r="F38">
         <v>1365</v>
@@ -2942,7 +2942,7 @@
         <v>14</v>
       </c>
       <c r="E39">
-        <v>0.24333750000000001</v>
+        <v>0.18980325000000003</v>
       </c>
       <c r="F39">
         <v>1365</v>
@@ -2998,7 +2998,7 @@
         <v>14</v>
       </c>
       <c r="E40">
-        <v>0.24333750000000001</v>
+        <v>0.18980325000000001</v>
       </c>
       <c r="F40">
         <v>1365</v>
@@ -3054,7 +3054,7 @@
         <v>14</v>
       </c>
       <c r="E41">
-        <v>0.26136249999999994</v>
+        <v>0.20386274999999998</v>
       </c>
       <c r="F41">
         <v>1365</v>
@@ -3110,7 +3110,7 @@
         <v>14</v>
       </c>
       <c r="E42">
-        <v>0.22981874999999999</v>
+        <v>0.179258625</v>
       </c>
       <c r="F42">
         <v>1365</v>
@@ -3166,7 +3166,7 @@
         <v>14</v>
       </c>
       <c r="E43">
-        <v>0.22981874999999999</v>
+        <v>0.179258625</v>
       </c>
       <c r="F43">
         <v>1365</v>
@@ -3222,7 +3222,7 @@
         <v>14</v>
       </c>
       <c r="E44">
-        <v>0.20728750000000001</v>
+        <v>0.16168425000000003</v>
       </c>
       <c r="F44">
         <v>1365</v>
@@ -3278,7 +3278,7 @@
         <v>14</v>
       </c>
       <c r="E45">
-        <v>0.20728750000000001</v>
+        <v>0.16168425000000003</v>
       </c>
       <c r="F45">
         <v>1365</v>
@@ -3334,7 +3334,7 @@
         <v>14</v>
       </c>
       <c r="E46">
-        <v>0.1892625</v>
+        <v>0.14762475</v>
       </c>
       <c r="F46">
         <v>1365</v>
@@ -3390,7 +3390,7 @@
         <v>14</v>
       </c>
       <c r="E47">
-        <v>0.26136249999999994</v>
+        <v>0.20386274999999998</v>
       </c>
       <c r="F47">
         <v>1365</v>
@@ -3446,7 +3446,7 @@
         <v>14</v>
       </c>
       <c r="E48">
-        <v>0.24333750000000001</v>
+        <v>0.18980325000000003</v>
       </c>
       <c r="F48">
         <v>1365</v>
@@ -3502,7 +3502,7 @@
         <v>14</v>
       </c>
       <c r="E49">
-        <v>0.1892625</v>
+        <v>0.14762475</v>
       </c>
       <c r="F49">
         <v>1365</v>
@@ -3558,7 +3558,7 @@
         <v>14</v>
       </c>
       <c r="E50">
-        <v>0.306425</v>
+        <v>0.23901150000000002</v>
       </c>
       <c r="F50">
         <v>1365</v>
@@ -3614,7 +3614,7 @@
         <v>14</v>
       </c>
       <c r="E51">
-        <v>0.28389375</v>
+        <v>0.22143712500000004</v>
       </c>
       <c r="F51">
         <v>1365</v>
@@ -3670,7 +3670,7 @@
         <v>14</v>
       </c>
       <c r="E52">
-        <v>0.306425</v>
+        <v>0.23901150000000002</v>
       </c>
       <c r="F52">
         <v>1365</v>
@@ -3726,7 +3726,7 @@
         <v>14</v>
       </c>
       <c r="E53">
-        <v>0.31543749999999998</v>
+        <v>0.24604124999999999</v>
       </c>
       <c r="F53">
         <v>1365</v>
@@ -3782,7 +3782,7 @@
         <v>14</v>
       </c>
       <c r="E54">
-        <v>0.31543749999999998</v>
+        <v>0.24604124999999999</v>
       </c>
       <c r="F54">
         <v>1365</v>
@@ -3838,7 +3838,7 @@
         <v>14</v>
       </c>
       <c r="E55">
-        <v>0.31543749999999998</v>
+        <v>0.24604124999999999</v>
       </c>
       <c r="F55">
         <v>1365</v>
@@ -3894,7 +3894,7 @@
         <v>14</v>
       </c>
       <c r="E56">
-        <v>0.28839999999999999</v>
+        <v>0.22495200000000004</v>
       </c>
       <c r="F56">
         <v>1365</v>
@@ -3950,7 +3950,7 @@
         <v>14</v>
       </c>
       <c r="E57">
-        <v>0.28839999999999999</v>
+        <v>0.22495200000000004</v>
       </c>
       <c r="F57">
         <v>1365</v>
@@ -4006,7 +4006,7 @@
         <v>14</v>
       </c>
       <c r="E58">
-        <v>0.26136249999999994</v>
+        <v>0.20386274999999998</v>
       </c>
       <c r="F58">
         <v>1365</v>
@@ -4062,7 +4062,7 @@
         <v>14</v>
       </c>
       <c r="E59">
-        <v>0.27037500000000003</v>
+        <v>0.21089250000000001</v>
       </c>
       <c r="F59">
         <v>1365</v>
@@ -4118,7 +4118,7 @@
         <v>14</v>
       </c>
       <c r="E60">
-        <v>0.27037500000000003</v>
+        <v>0.21089250000000001</v>
       </c>
       <c r="F60">
         <v>1365</v>
@@ -4174,7 +4174,7 @@
         <v>14</v>
       </c>
       <c r="E61">
-        <v>0.26136249999999994</v>
+        <v>0.20386274999999998</v>
       </c>
       <c r="F61">
         <v>1365</v>
@@ -4230,7 +4230,7 @@
         <v>14</v>
       </c>
       <c r="E62">
-        <v>0.30191875000000001</v>
+        <v>0.23549662500000001</v>
       </c>
       <c r="F62">
         <v>1365</v>
@@ -4281,7 +4281,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD445F59-4A10-4FF0-80B5-2184A2348430}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB8CADC3-F2CC-466B-9DA1-164922B2F7DA}">
   <dimension ref="B9:T124"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4366,7 +4366,7 @@
         <v>0.13</v>
       </c>
       <c r="G11">
-        <v>0.33990000000000004</v>
+        <v>0.26512200000000002</v>
       </c>
       <c r="H11">
         <v>4427.5</v>
@@ -6539,7 +6539,7 @@
         <v>0.13300000000000001</v>
       </c>
       <c r="G52">
-        <v>0.49440000000000001</v>
+        <v>0.38563200000000003</v>
       </c>
       <c r="H52">
         <v>1391.5</v>
@@ -6592,7 +6592,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="G53">
-        <v>0.42230000000000001</v>
+        <v>0.32939400000000002</v>
       </c>
       <c r="H53">
         <v>1391.5</v>
@@ -6645,7 +6645,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="G54">
-        <v>0.42230000000000001</v>
+        <v>0.32939400000000002</v>
       </c>
       <c r="H54">
         <v>1391.5</v>
@@ -6698,7 +6698,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="G55">
-        <v>0.27810000000000001</v>
+        <v>0.21691800000000003</v>
       </c>
       <c r="H55">
         <v>1336.5</v>
@@ -6751,7 +6751,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="G56">
-        <v>0.27810000000000001</v>
+        <v>0.21691800000000003</v>
       </c>
       <c r="H56">
         <v>1336.5</v>
@@ -6804,7 +6804,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="G57">
-        <v>0.27810000000000001</v>
+        <v>0.216918</v>
       </c>
       <c r="H57">
         <v>1336.5</v>
@@ -6857,7 +6857,7 @@
         <v>0.02</v>
       </c>
       <c r="G58">
-        <v>0.29869999999999997</v>
+        <v>0.23298599999999997</v>
       </c>
       <c r="H58">
         <v>1336.5</v>
@@ -6910,7 +6910,7 @@
         <v>0.06</v>
       </c>
       <c r="G59">
-        <v>0.26264999999999999</v>
+        <v>0.20486699999999999</v>
       </c>
       <c r="H59">
         <v>1138.5</v>
@@ -6963,7 +6963,7 @@
         <v>0.06</v>
       </c>
       <c r="G60">
-        <v>0.26264999999999999</v>
+        <v>0.20486699999999999</v>
       </c>
       <c r="H60">
         <v>1138.5</v>
@@ -7016,7 +7016,7 @@
         <v>2.4E-2</v>
       </c>
       <c r="G61">
-        <v>0.23690000000000003</v>
+        <v>0.18478200000000003</v>
       </c>
       <c r="H61">
         <v>1336.5</v>
@@ -7069,7 +7069,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="G62">
-        <v>0.23690000000000003</v>
+        <v>0.18478200000000003</v>
       </c>
       <c r="H62">
         <v>1336.5</v>
@@ -7122,7 +7122,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="G63">
-        <v>0.21629999999999999</v>
+        <v>0.168714</v>
       </c>
       <c r="H63">
         <v>1336.5</v>
@@ -7175,7 +7175,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G64">
-        <v>0.29869999999999997</v>
+        <v>0.23298599999999997</v>
       </c>
       <c r="H64">
         <v>1336.5</v>
@@ -7228,7 +7228,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="G65">
-        <v>0.27810000000000001</v>
+        <v>0.21691800000000003</v>
       </c>
       <c r="H65">
         <v>1336.5</v>
@@ -7281,7 +7281,7 @@
         <v>0.03</v>
       </c>
       <c r="G66">
-        <v>0.21629999999999999</v>
+        <v>0.168714</v>
       </c>
       <c r="H66">
         <v>1336.5</v>
@@ -7334,7 +7334,7 @@
         <v>0.104</v>
       </c>
       <c r="G67">
-        <v>0.35020000000000001</v>
+        <v>0.27315600000000001</v>
       </c>
       <c r="H67">
         <v>1265</v>
@@ -7387,7 +7387,7 @@
         <v>0.05</v>
       </c>
       <c r="G68">
-        <v>0.32445000000000002</v>
+        <v>0.25307100000000005</v>
       </c>
       <c r="H68">
         <v>1485.0000000000002</v>
@@ -7440,7 +7440,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="G69">
-        <v>0.35020000000000001</v>
+        <v>0.27315600000000001</v>
       </c>
       <c r="H69">
         <v>1485.0000000000002</v>
@@ -7493,7 +7493,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="G70">
-        <v>0.36049999999999999</v>
+        <v>0.28119</v>
       </c>
       <c r="H70">
         <v>1485.0000000000002</v>
@@ -7546,7 +7546,7 @@
         <v>0.12</v>
       </c>
       <c r="G71">
-        <v>0.36049999999999999</v>
+        <v>0.28119</v>
       </c>
       <c r="H71">
         <v>1265</v>
@@ -7599,7 +7599,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="G72">
-        <v>0.36049999999999999</v>
+        <v>0.28119</v>
       </c>
       <c r="H72">
         <v>1485.0000000000002</v>
@@ -7652,7 +7652,7 @@
         <v>0.05</v>
       </c>
       <c r="G73">
-        <v>0.3296</v>
+        <v>0.25708800000000004</v>
       </c>
       <c r="H73">
         <v>1930.5000000000007</v>
@@ -7705,7 +7705,7 @@
         <v>0.05</v>
       </c>
       <c r="G74">
-        <v>0.3296</v>
+        <v>0.25708800000000004</v>
       </c>
       <c r="H74">
         <v>1930.5000000000007</v>
@@ -7758,7 +7758,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G75">
-        <v>0.29869999999999997</v>
+        <v>0.23298599999999997</v>
       </c>
       <c r="H75">
         <v>1930.5000000000007</v>
@@ -7811,7 +7811,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G76">
-        <v>0.309</v>
+        <v>0.24102000000000001</v>
       </c>
       <c r="H76">
         <v>1930.5000000000007</v>
@@ -7864,7 +7864,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G77">
-        <v>0.309</v>
+        <v>0.24102000000000001</v>
       </c>
       <c r="H77">
         <v>1930.5000000000007</v>
@@ -7917,7 +7917,7 @@
         <v>0.03</v>
       </c>
       <c r="G78">
-        <v>0.29869999999999997</v>
+        <v>0.23298599999999997</v>
       </c>
       <c r="H78">
         <v>1930.5000000000005</v>
@@ -7970,7 +7970,7 @@
         <v>0.17399999999999999</v>
       </c>
       <c r="G79">
-        <v>0.34505000000000002</v>
+        <v>0.26913900000000002</v>
       </c>
       <c r="H79">
         <v>1644.4999999999998</v>

--- a/VerveStacks_GRC/vt_vervestacks_GRC_v1.xlsx
+++ b/VerveStacks_GRC/vt_vervestacks_GRC_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GRC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B3A0345-39F8-4FCE-B0DE-EEFA73516610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0CEF3865-2E0D-47F4-A75F-5C28F973785C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{262781E9-7CE6-4CF1-84F4-03993671DA64}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{470F5E59-426B-4CE1-8DD3-325DF0EDBF9B}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -1295,7 +1295,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C2AE76D-B5E7-4F9D-99A6-B1749C5525BC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB1C8CAD-0996-4E11-9405-114C116BA82D}">
   <dimension ref="B9:T62"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1374,7 +1374,7 @@
         <v>14</v>
       </c>
       <c r="E11">
-        <v>8.5481760000000018E-2</v>
+        <v>8.7673600000000018E-2</v>
       </c>
       <c r="F11">
         <v>3583</v>
@@ -1430,7 +1430,7 @@
         <v>14</v>
       </c>
       <c r="E12">
-        <v>8.5481760000000018E-2</v>
+        <v>8.7673600000000018E-2</v>
       </c>
       <c r="F12">
         <v>3583</v>
@@ -1486,7 +1486,7 @@
         <v>14</v>
       </c>
       <c r="E13">
-        <v>8.7924096000000021E-2</v>
+        <v>9.0178560000000019E-2</v>
       </c>
       <c r="F13">
         <v>3583</v>
@@ -1542,7 +1542,7 @@
         <v>14</v>
       </c>
       <c r="E14">
-        <v>0.12689702999999999</v>
+        <v>0.13015080000000001</v>
       </c>
       <c r="F14">
         <v>3144</v>
@@ -1598,7 +1598,7 @@
         <v>14</v>
       </c>
       <c r="E15">
-        <v>0.12852391500000002</v>
+        <v>0.13181940000000003</v>
       </c>
       <c r="F15">
         <v>3144</v>
@@ -1654,7 +1654,7 @@
         <v>14</v>
       </c>
       <c r="E16">
-        <v>0.272782419</v>
+        <v>0.27977684000000003</v>
       </c>
       <c r="F16">
         <v>1967</v>
@@ -1710,7 +1710,7 @@
         <v>14</v>
       </c>
       <c r="E17">
-        <v>0.40772549999999996</v>
+        <v>0.41818</v>
       </c>
       <c r="F17">
         <v>1365</v>
@@ -1766,7 +1766,7 @@
         <v>14</v>
       </c>
       <c r="E18">
-        <v>0.38312137500000004</v>
+        <v>0.39294500000000004</v>
       </c>
       <c r="F18">
         <v>1365</v>
@@ -1822,7 +1822,7 @@
         <v>14</v>
       </c>
       <c r="E19">
-        <v>0.42178500000000002</v>
+        <v>0.43259999999999998</v>
       </c>
       <c r="F19">
         <v>1365</v>
@@ -1878,7 +1878,7 @@
         <v>14</v>
       </c>
       <c r="E20">
-        <v>0.40772549999999996</v>
+        <v>0.41818</v>
       </c>
       <c r="F20">
         <v>1365</v>
@@ -1934,7 +1934,7 @@
         <v>14</v>
       </c>
       <c r="E21">
-        <v>0.40772549999999996</v>
+        <v>0.41817999999999989</v>
       </c>
       <c r="F21">
         <v>1365</v>
@@ -1990,7 +1990,7 @@
         <v>14</v>
       </c>
       <c r="E22">
-        <v>0.38312137500000004</v>
+        <v>0.39294500000000004</v>
       </c>
       <c r="F22">
         <v>1365</v>
@@ -2046,7 +2046,7 @@
         <v>14</v>
       </c>
       <c r="E23">
-        <v>0.36906187500000009</v>
+        <v>0.37852500000000006</v>
       </c>
       <c r="F23">
         <v>1365</v>
@@ -2102,7 +2102,7 @@
         <v>14</v>
       </c>
       <c r="E24">
-        <v>0.38312137500000004</v>
+        <v>0.39294499999999999</v>
       </c>
       <c r="F24">
         <v>1365</v>
@@ -2158,7 +2158,7 @@
         <v>14</v>
       </c>
       <c r="E25">
-        <v>0.38312137500000004</v>
+        <v>0.39294500000000004</v>
       </c>
       <c r="F25">
         <v>1365</v>
@@ -2214,7 +2214,7 @@
         <v>14</v>
       </c>
       <c r="E26">
-        <v>0.38312137500000004</v>
+        <v>0.39294500000000004</v>
       </c>
       <c r="F26">
         <v>1365</v>
@@ -2270,7 +2270,7 @@
         <v>14</v>
       </c>
       <c r="E27">
-        <v>0.38312137500000004</v>
+        <v>0.39294500000000004</v>
       </c>
       <c r="F27">
         <v>1365</v>
@@ -2326,7 +2326,7 @@
         <v>14</v>
       </c>
       <c r="E28">
-        <v>0.42178500000000002</v>
+        <v>0.43259999999999998</v>
       </c>
       <c r="F28">
         <v>1365</v>
@@ -2382,7 +2382,7 @@
         <v>14</v>
       </c>
       <c r="E29">
-        <v>0.42178500000000008</v>
+        <v>0.43259999999999998</v>
       </c>
       <c r="F29">
         <v>1365</v>
@@ -2438,7 +2438,7 @@
         <v>14</v>
       </c>
       <c r="E30">
-        <v>0.40772549999999996</v>
+        <v>0.41818</v>
       </c>
       <c r="F30">
         <v>1365</v>
@@ -2494,7 +2494,7 @@
         <v>14</v>
       </c>
       <c r="E31">
-        <v>0.42178500000000002</v>
+        <v>0.43259999999999998</v>
       </c>
       <c r="F31">
         <v>1365</v>
@@ -2550,7 +2550,7 @@
         <v>14</v>
       </c>
       <c r="E32">
-        <v>0.19683300000000004</v>
+        <v>0.20188000000000003</v>
       </c>
       <c r="F32">
         <v>1365</v>
@@ -2606,7 +2606,7 @@
         <v>14</v>
       </c>
       <c r="E33">
-        <v>0.19683300000000004</v>
+        <v>0.20188000000000003</v>
       </c>
       <c r="F33">
         <v>1365</v>
@@ -2662,7 +2662,7 @@
         <v>14</v>
       </c>
       <c r="E34">
-        <v>0.19683300000000004</v>
+        <v>0.20188000000000003</v>
       </c>
       <c r="F34">
         <v>1365</v>
@@ -2718,7 +2718,7 @@
         <v>14</v>
       </c>
       <c r="E35">
-        <v>0.33742800000000001</v>
+        <v>0.34608000000000005</v>
       </c>
       <c r="F35">
         <v>1365</v>
@@ -2774,7 +2774,7 @@
         <v>14</v>
       </c>
       <c r="E36">
-        <v>0.28821975</v>
+        <v>0.29561000000000004</v>
       </c>
       <c r="F36">
         <v>1365</v>
@@ -2830,7 +2830,7 @@
         <v>14</v>
       </c>
       <c r="E37">
-        <v>0.28821975</v>
+        <v>0.29561000000000004</v>
       </c>
       <c r="F37">
         <v>1365</v>
@@ -2886,7 +2886,7 @@
         <v>14</v>
       </c>
       <c r="E38">
-        <v>0.18980325000000003</v>
+        <v>0.19467000000000001</v>
       </c>
       <c r="F38">
         <v>1365</v>
@@ -2942,7 +2942,7 @@
         <v>14</v>
       </c>
       <c r="E39">
-        <v>0.18980325000000003</v>
+        <v>0.19467000000000001</v>
       </c>
       <c r="F39">
         <v>1365</v>
@@ -2998,7 +2998,7 @@
         <v>14</v>
       </c>
       <c r="E40">
-        <v>0.18980325000000001</v>
+        <v>0.19466999999999998</v>
       </c>
       <c r="F40">
         <v>1365</v>
@@ -3054,7 +3054,7 @@
         <v>14</v>
       </c>
       <c r="E41">
-        <v>0.20386274999999998</v>
+        <v>0.20909</v>
       </c>
       <c r="F41">
         <v>1365</v>
@@ -3110,7 +3110,7 @@
         <v>14</v>
       </c>
       <c r="E42">
-        <v>0.179258625</v>
+        <v>0.18385499999999999</v>
       </c>
       <c r="F42">
         <v>1365</v>
@@ -3166,7 +3166,7 @@
         <v>14</v>
       </c>
       <c r="E43">
-        <v>0.179258625</v>
+        <v>0.18385499999999999</v>
       </c>
       <c r="F43">
         <v>1365</v>
@@ -3222,7 +3222,7 @@
         <v>14</v>
       </c>
       <c r="E44">
-        <v>0.16168425000000003</v>
+        <v>0.16583000000000003</v>
       </c>
       <c r="F44">
         <v>1365</v>
@@ -3278,7 +3278,7 @@
         <v>14</v>
       </c>
       <c r="E45">
-        <v>0.16168425000000003</v>
+        <v>0.16583000000000003</v>
       </c>
       <c r="F45">
         <v>1365</v>
@@ -3334,7 +3334,7 @@
         <v>14</v>
       </c>
       <c r="E46">
-        <v>0.14762475</v>
+        <v>0.15140999999999999</v>
       </c>
       <c r="F46">
         <v>1365</v>
@@ -3390,7 +3390,7 @@
         <v>14</v>
       </c>
       <c r="E47">
-        <v>0.20386274999999998</v>
+        <v>0.20909</v>
       </c>
       <c r="F47">
         <v>1365</v>
@@ -3446,7 +3446,7 @@
         <v>14</v>
       </c>
       <c r="E48">
-        <v>0.18980325000000003</v>
+        <v>0.19467000000000001</v>
       </c>
       <c r="F48">
         <v>1365</v>
@@ -3502,7 +3502,7 @@
         <v>14</v>
       </c>
       <c r="E49">
-        <v>0.14762475</v>
+        <v>0.15140999999999999</v>
       </c>
       <c r="F49">
         <v>1365</v>
@@ -3558,7 +3558,7 @@
         <v>14</v>
       </c>
       <c r="E50">
-        <v>0.23901150000000002</v>
+        <v>0.24514000000000002</v>
       </c>
       <c r="F50">
         <v>1365</v>
@@ -3614,7 +3614,7 @@
         <v>14</v>
       </c>
       <c r="E51">
-        <v>0.22143712500000004</v>
+        <v>0.22711500000000001</v>
       </c>
       <c r="F51">
         <v>1365</v>
@@ -3670,7 +3670,7 @@
         <v>14</v>
       </c>
       <c r="E52">
-        <v>0.23901150000000002</v>
+        <v>0.24514000000000002</v>
       </c>
       <c r="F52">
         <v>1365</v>
@@ -3726,7 +3726,7 @@
         <v>14</v>
       </c>
       <c r="E53">
-        <v>0.24604124999999999</v>
+        <v>0.25235000000000002</v>
       </c>
       <c r="F53">
         <v>1365</v>
@@ -3782,7 +3782,7 @@
         <v>14</v>
       </c>
       <c r="E54">
-        <v>0.24604124999999999</v>
+        <v>0.25235000000000002</v>
       </c>
       <c r="F54">
         <v>1365</v>
@@ -3838,7 +3838,7 @@
         <v>14</v>
       </c>
       <c r="E55">
-        <v>0.24604124999999999</v>
+        <v>0.25235000000000002</v>
       </c>
       <c r="F55">
         <v>1365</v>
@@ -3894,7 +3894,7 @@
         <v>14</v>
       </c>
       <c r="E56">
-        <v>0.22495200000000004</v>
+        <v>0.23072000000000004</v>
       </c>
       <c r="F56">
         <v>1365</v>
@@ -3950,7 +3950,7 @@
         <v>14</v>
       </c>
       <c r="E57">
-        <v>0.22495200000000004</v>
+        <v>0.23072000000000004</v>
       </c>
       <c r="F57">
         <v>1365</v>
@@ -4006,7 +4006,7 @@
         <v>14</v>
       </c>
       <c r="E58">
-        <v>0.20386274999999998</v>
+        <v>0.20909</v>
       </c>
       <c r="F58">
         <v>1365</v>
@@ -4062,7 +4062,7 @@
         <v>14</v>
       </c>
       <c r="E59">
-        <v>0.21089250000000001</v>
+        <v>0.21629999999999999</v>
       </c>
       <c r="F59">
         <v>1365</v>
@@ -4118,7 +4118,7 @@
         <v>14</v>
       </c>
       <c r="E60">
-        <v>0.21089250000000001</v>
+        <v>0.21629999999999999</v>
       </c>
       <c r="F60">
         <v>1365</v>
@@ -4174,7 +4174,7 @@
         <v>14</v>
       </c>
       <c r="E61">
-        <v>0.20386274999999998</v>
+        <v>0.20909</v>
       </c>
       <c r="F61">
         <v>1365</v>
@@ -4230,7 +4230,7 @@
         <v>14</v>
       </c>
       <c r="E62">
-        <v>0.23549662500000001</v>
+        <v>0.241535</v>
       </c>
       <c r="F62">
         <v>1365</v>
@@ -4281,7 +4281,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB8CADC3-F2CC-466B-9DA1-164922B2F7DA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5371DC18-08DE-4166-819B-845A696B22D5}">
   <dimension ref="B9:T124"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4366,7 +4366,7 @@
         <v>0.13</v>
       </c>
       <c r="G11">
-        <v>0.26512200000000002</v>
+        <v>0.27192000000000005</v>
       </c>
       <c r="H11">
         <v>4427.5</v>
@@ -4419,7 +4419,7 @@
         <v>0.89500000000000024</v>
       </c>
       <c r="G12">
-        <v>0.28922400000000004</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H12">
         <v>2200</v>
@@ -4472,7 +4472,7 @@
         <v>0.31</v>
       </c>
       <c r="G13">
-        <v>0.28119</v>
+        <v>0.28839999999999999</v>
       </c>
       <c r="H13">
         <v>2200</v>
@@ -4525,7 +4525,7 @@
         <v>0.31</v>
       </c>
       <c r="G14">
-        <v>0.28119</v>
+        <v>0.28839999999999999</v>
       </c>
       <c r="H14">
         <v>2200</v>
@@ -4578,7 +4578,7 @@
         <v>0.375</v>
       </c>
       <c r="G15">
-        <v>0.31332599999999999</v>
+        <v>0.32136000000000003</v>
       </c>
       <c r="H15">
         <v>2420</v>
@@ -4631,7 +4631,7 @@
         <v>0.33</v>
       </c>
       <c r="G16">
-        <v>0.31734300000000004</v>
+        <v>0.32548000000000005</v>
       </c>
       <c r="H16">
         <v>2420</v>
@@ -4684,7 +4684,7 @@
         <v>0.66</v>
       </c>
       <c r="G17">
-        <v>0.35751300000000003</v>
+        <v>0.36668000000000006</v>
       </c>
       <c r="H17">
         <v>2640</v>
@@ -4737,7 +4737,7 @@
         <v>1.0463999999999993</v>
       </c>
       <c r="G18">
-        <v>0.48204000000000002</v>
+        <v>0.49440000000000001</v>
       </c>
       <c r="H18">
         <v>1100</v>
@@ -4790,7 +4790,7 @@
         <v>0.44400000000000001</v>
       </c>
       <c r="G19">
-        <v>0.46597199999999994</v>
+        <v>0.47791999999999996</v>
       </c>
       <c r="H19">
         <v>1100</v>
@@ -4843,7 +4843,7 @@
         <v>0.33400000000000002</v>
       </c>
       <c r="G20">
-        <v>0.43785300000000005</v>
+        <v>0.44908000000000003</v>
       </c>
       <c r="H20">
         <v>1100</v>
@@ -4896,7 +4896,7 @@
         <v>0.82599999999999996</v>
       </c>
       <c r="G21">
-        <v>0.48204000000000002</v>
+        <v>0.49439999999999995</v>
       </c>
       <c r="H21">
         <v>1100</v>
@@ -4949,7 +4949,7 @@
         <v>0.41699999999999998</v>
       </c>
       <c r="G22">
-        <v>0.46597199999999994</v>
+        <v>0.47791999999999996</v>
       </c>
       <c r="H22">
         <v>1100</v>
@@ -5002,7 +5002,7 @@
         <v>0.43660000000000004</v>
       </c>
       <c r="G23">
-        <v>0.46597199999999994</v>
+        <v>0.4779199999999999</v>
       </c>
       <c r="H23">
         <v>1100</v>
@@ -5055,7 +5055,7 @@
         <v>0.48499999999999999</v>
       </c>
       <c r="G24">
-        <v>0.43785300000000005</v>
+        <v>0.44908000000000003</v>
       </c>
       <c r="H24">
         <v>1100</v>
@@ -5108,7 +5108,7 @@
         <v>0.53600000000000003</v>
       </c>
       <c r="G25">
-        <v>0.42178500000000008</v>
+        <v>0.4326000000000001</v>
       </c>
       <c r="H25">
         <v>1100</v>
@@ -5161,7 +5161,7 @@
         <v>0.378</v>
       </c>
       <c r="G26">
-        <v>0.43785300000000005</v>
+        <v>0.44907999999999998</v>
       </c>
       <c r="H26">
         <v>1100</v>
@@ -5214,7 +5214,7 @@
         <v>0.42</v>
       </c>
       <c r="G27">
-        <v>0.43785300000000005</v>
+        <v>0.44908000000000003</v>
       </c>
       <c r="H27">
         <v>1100</v>
@@ -5267,7 +5267,7 @@
         <v>0.42</v>
       </c>
       <c r="G28">
-        <v>0.43785300000000005</v>
+        <v>0.44908000000000003</v>
       </c>
       <c r="H28">
         <v>1100</v>
@@ -5320,7 +5320,7 @@
         <v>0.435</v>
       </c>
       <c r="G29">
-        <v>0.43785300000000005</v>
+        <v>0.44908000000000003</v>
       </c>
       <c r="H29">
         <v>1100</v>
@@ -5373,7 +5373,7 @@
         <v>0.84</v>
       </c>
       <c r="G30">
-        <v>0.48204000000000002</v>
+        <v>0.49440000000000001</v>
       </c>
       <c r="H30">
         <v>1100</v>
@@ -5426,7 +5426,7 @@
         <v>0.877</v>
       </c>
       <c r="G31">
-        <v>0.48204000000000008</v>
+        <v>0.49440000000000001</v>
       </c>
       <c r="H31">
         <v>1100</v>
@@ -5479,7 +5479,7 @@
         <v>0.81100000000000005</v>
       </c>
       <c r="G32">
-        <v>0.46597199999999994</v>
+        <v>0.47791999999999996</v>
       </c>
       <c r="H32">
         <v>1100</v>
@@ -5532,7 +5532,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="G33">
-        <v>0.22495200000000004</v>
+        <v>0.23072000000000004</v>
       </c>
       <c r="H33">
         <v>1188</v>
@@ -5585,7 +5585,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="G34">
-        <v>0.22495200000000004</v>
+        <v>0.23072000000000004</v>
       </c>
       <c r="H34">
         <v>1188</v>
@@ -5638,7 +5638,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="G35">
-        <v>0.22495200000000004</v>
+        <v>0.23072000000000004</v>
       </c>
       <c r="H35">
         <v>1188</v>
@@ -6539,7 +6539,7 @@
         <v>0.13300000000000001</v>
       </c>
       <c r="G52">
-        <v>0.38563200000000003</v>
+        <v>0.39552000000000004</v>
       </c>
       <c r="H52">
         <v>1391.5</v>
@@ -6592,7 +6592,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="G53">
-        <v>0.32939400000000002</v>
+        <v>0.33784000000000003</v>
       </c>
       <c r="H53">
         <v>1391.5</v>
@@ -6645,7 +6645,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="G54">
-        <v>0.32939400000000002</v>
+        <v>0.33784000000000003</v>
       </c>
       <c r="H54">
         <v>1391.5</v>
@@ -6698,7 +6698,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="G55">
-        <v>0.21691800000000003</v>
+        <v>0.22248000000000001</v>
       </c>
       <c r="H55">
         <v>1336.5</v>
@@ -6751,7 +6751,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="G56">
-        <v>0.21691800000000003</v>
+        <v>0.22248000000000001</v>
       </c>
       <c r="H56">
         <v>1336.5</v>
@@ -6804,7 +6804,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="G57">
-        <v>0.216918</v>
+        <v>0.22247999999999998</v>
       </c>
       <c r="H57">
         <v>1336.5</v>
@@ -6857,7 +6857,7 @@
         <v>0.02</v>
       </c>
       <c r="G58">
-        <v>0.23298599999999997</v>
+        <v>0.23895999999999998</v>
       </c>
       <c r="H58">
         <v>1336.5</v>
@@ -6910,7 +6910,7 @@
         <v>0.06</v>
       </c>
       <c r="G59">
-        <v>0.20486699999999999</v>
+        <v>0.21012</v>
       </c>
       <c r="H59">
         <v>1138.5</v>
@@ -6963,7 +6963,7 @@
         <v>0.06</v>
       </c>
       <c r="G60">
-        <v>0.20486699999999999</v>
+        <v>0.21012</v>
       </c>
       <c r="H60">
         <v>1138.5</v>
@@ -7016,7 +7016,7 @@
         <v>2.4E-2</v>
       </c>
       <c r="G61">
-        <v>0.18478200000000003</v>
+        <v>0.18952000000000002</v>
       </c>
       <c r="H61">
         <v>1336.5</v>
@@ -7069,7 +7069,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="G62">
-        <v>0.18478200000000003</v>
+        <v>0.18952000000000002</v>
       </c>
       <c r="H62">
         <v>1336.5</v>
@@ -7122,7 +7122,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="G63">
-        <v>0.168714</v>
+        <v>0.17304</v>
       </c>
       <c r="H63">
         <v>1336.5</v>
@@ -7175,7 +7175,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G64">
-        <v>0.23298599999999997</v>
+        <v>0.23895999999999998</v>
       </c>
       <c r="H64">
         <v>1336.5</v>
@@ -7228,7 +7228,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="G65">
-        <v>0.21691800000000003</v>
+        <v>0.22248000000000001</v>
       </c>
       <c r="H65">
         <v>1336.5</v>
@@ -7281,7 +7281,7 @@
         <v>0.03</v>
       </c>
       <c r="G66">
-        <v>0.168714</v>
+        <v>0.17304</v>
       </c>
       <c r="H66">
         <v>1336.5</v>
@@ -7334,7 +7334,7 @@
         <v>0.104</v>
       </c>
       <c r="G67">
-        <v>0.27315600000000001</v>
+        <v>0.28016000000000002</v>
       </c>
       <c r="H67">
         <v>1265</v>
@@ -7387,7 +7387,7 @@
         <v>0.05</v>
       </c>
       <c r="G68">
-        <v>0.25307100000000005</v>
+        <v>0.25956000000000001</v>
       </c>
       <c r="H68">
         <v>1485.0000000000002</v>
@@ -7440,7 +7440,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="G69">
-        <v>0.27315600000000001</v>
+        <v>0.28016000000000002</v>
       </c>
       <c r="H69">
         <v>1485.0000000000002</v>
@@ -7493,7 +7493,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="G70">
-        <v>0.28119</v>
+        <v>0.28839999999999999</v>
       </c>
       <c r="H70">
         <v>1485.0000000000002</v>
@@ -7546,7 +7546,7 @@
         <v>0.12</v>
       </c>
       <c r="G71">
-        <v>0.28119</v>
+        <v>0.28839999999999999</v>
       </c>
       <c r="H71">
         <v>1265</v>
@@ -7599,7 +7599,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="G72">
-        <v>0.28119</v>
+        <v>0.28839999999999999</v>
       </c>
       <c r="H72">
         <v>1485.0000000000002</v>
@@ -7652,7 +7652,7 @@
         <v>0.05</v>
       </c>
       <c r="G73">
-        <v>0.25708800000000004</v>
+        <v>0.26368000000000003</v>
       </c>
       <c r="H73">
         <v>1930.5000000000007</v>
@@ -7705,7 +7705,7 @@
         <v>0.05</v>
       </c>
       <c r="G74">
-        <v>0.25708800000000004</v>
+        <v>0.26368000000000003</v>
       </c>
       <c r="H74">
         <v>1930.5000000000007</v>
@@ -7758,7 +7758,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G75">
-        <v>0.23298599999999997</v>
+        <v>0.23895999999999998</v>
       </c>
       <c r="H75">
         <v>1930.5000000000007</v>
@@ -7811,7 +7811,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G76">
-        <v>0.24102000000000001</v>
+        <v>0.24719999999999998</v>
       </c>
       <c r="H76">
         <v>1930.5000000000007</v>
@@ -7864,7 +7864,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G77">
-        <v>0.24102000000000001</v>
+        <v>0.24719999999999998</v>
       </c>
       <c r="H77">
         <v>1930.5000000000007</v>
@@ -7917,7 +7917,7 @@
         <v>0.03</v>
       </c>
       <c r="G78">
-        <v>0.23298599999999997</v>
+        <v>0.23895999999999998</v>
       </c>
       <c r="H78">
         <v>1930.5000000000005</v>
@@ -7970,7 +7970,7 @@
         <v>0.17399999999999999</v>
       </c>
       <c r="G79">
-        <v>0.26913900000000002</v>
+        <v>0.27604000000000001</v>
       </c>
       <c r="H79">
         <v>1644.4999999999998</v>
@@ -8038,7 +8038,7 @@
         <v>33</v>
       </c>
       <c r="L80">
-        <v>0.21430892696649589</v>
+        <v>0.21430892696649592</v>
       </c>
       <c r="N80" t="s">
         <v>106</v>
